--- a/src/v1/Services/MasterFile-Sept&Oct_Update.xlsx
+++ b/src/v1/Services/MasterFile-Sept&Oct_Update.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Customer" sheetId="2" r:id="rId1"/>
+    <sheet name="Area" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Customer!$A$1:$X$190</definedName>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2103" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2170" uniqueCount="492">
   <si>
     <t>Mithun Das</t>
   </si>
@@ -393,9 +395,6 @@
     <t>Rajjak Hossin Molla</t>
   </si>
   <si>
-    <t xml:space="preserve"> Paschim Sitakundu</t>
-  </si>
-  <si>
     <t>Kantatala, Tardaha,  Kapasati,  South 24 pgs</t>
   </si>
   <si>
@@ -1504,13 +1503,19 @@
   </si>
   <si>
     <t>003</t>
+  </si>
+  <si>
+    <t>Lakshmanpur</t>
+  </si>
+  <si>
+    <t>Paschim Sitakundu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1537,8 +1542,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="MS Sans Serif"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1563,8 +1578,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1587,11 +1608,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="22"/>
+      </left>
+      <right style="thin">
+        <color indexed="22"/>
+      </right>
+      <top style="thin">
+        <color indexed="22"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1651,11 +1703,48 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal_Sheet1" xfId="1"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <condense val="0"/>
@@ -1983,7 +2072,8 @@
   <cols>
     <col min="1" max="1" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.42578125" style="2" customWidth="1"/>
     <col min="7" max="7" width="11.7109375" style="2" customWidth="1"/>
@@ -1991,7 +2081,7 @@
     <col min="9" max="9" width="12.42578125" style="2" customWidth="1"/>
     <col min="10" max="10" width="12.140625" style="2" customWidth="1"/>
     <col min="11" max="11" width="9.42578125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="40.28515625" style="2" customWidth="1"/>
     <col min="13" max="13" width="9" style="2" customWidth="1"/>
     <col min="14" max="14" width="5.7109375" style="2" customWidth="1"/>
     <col min="15" max="15" width="19.42578125" style="2" customWidth="1"/>
@@ -2086,31 +2176,31 @@
         <v>78</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L2" s="1">
         <v>9851656320</v>
@@ -2130,28 +2220,28 @@
         <v>96</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L3" s="1">
         <v>8582872056</v>
@@ -2174,25 +2264,25 @@
         <v>52</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>248</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L4" s="1">
         <v>9163118557</v>
@@ -2201,7 +2291,7 @@
         <v>26786</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -2215,25 +2305,25 @@
         <v>52</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>250</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L5" s="1">
         <v>8101920457</v>
@@ -2242,7 +2332,7 @@
         <v>36242</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -2250,31 +2340,31 @@
         <v>78</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>252</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L6" s="1">
         <v>9831896972</v>
@@ -2283,7 +2373,7 @@
         <v>29707</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -2294,28 +2384,28 @@
         <v>116</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>255</v>
-      </c>
       <c r="I7" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L7" s="1">
         <v>9836460462</v>
@@ -2324,7 +2414,7 @@
         <v>31312</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -2335,28 +2425,28 @@
         <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>117</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L8" s="1">
         <v>9874032353</v>
@@ -2365,7 +2455,7 @@
         <v>35892</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -2376,28 +2466,28 @@
         <v>116</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>259</v>
-      </c>
       <c r="I9" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L9" s="1">
         <v>8169056469</v>
@@ -2406,7 +2496,7 @@
         <v>36587</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -2420,25 +2510,25 @@
         <v>80</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L10" s="1">
         <v>7003820600</v>
@@ -2461,25 +2551,25 @@
         <v>80</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>81</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L11" s="1">
         <v>8697922405</v>
@@ -2488,7 +2578,7 @@
         <v>38718</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="1:24">
@@ -2502,25 +2592,25 @@
         <v>83</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L12" s="2">
         <v>8274060554</v>
@@ -2543,25 +2633,25 @@
         <v>80</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>85</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L13" s="2">
         <v>9836234291</v>
@@ -2570,7 +2660,7 @@
         <v>23743</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:24">
@@ -2584,25 +2674,25 @@
         <v>83</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L14" s="2">
         <v>7596942795</v>
@@ -2625,25 +2715,25 @@
         <v>83</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L15" s="2">
         <v>9831290038</v>
@@ -2666,25 +2756,25 @@
         <v>90</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>48</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L16" s="2">
         <v>8509544268</v>
@@ -2693,7 +2783,7 @@
         <v>35225</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -2707,25 +2797,25 @@
         <v>88</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L17" s="2">
         <v>6296745551</v>
@@ -2748,25 +2838,25 @@
         <v>52</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>95</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>94</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L18" s="2">
         <v>7029983005</v>
@@ -2775,7 +2865,7 @@
         <v>31908</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -2789,25 +2879,25 @@
         <v>52</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>97</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>99</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L19" s="2">
         <v>9264807129</v>
@@ -2816,7 +2906,7 @@
         <v>38575</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -2830,25 +2920,25 @@
         <v>52</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>98</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>100</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L20" s="2">
         <v>9836729202</v>
@@ -2871,25 +2961,25 @@
         <v>52</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>102</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>101</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L21" s="2">
         <v>9073045833</v>
@@ -2912,25 +3002,25 @@
         <v>106</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>105</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L22" s="2">
         <v>7044288518</v>
@@ -2939,7 +3029,7 @@
         <v>33461</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -2953,25 +3043,25 @@
         <v>108</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>109</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>110</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L23" s="2">
         <v>8697751239</v>
@@ -2994,25 +3084,25 @@
         <v>113</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>112</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>111</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L24" s="2">
         <v>8017555832</v>
@@ -3021,7 +3111,7 @@
         <v>38718</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -3035,25 +3125,25 @@
         <v>115</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>114</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>117</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L25" s="2">
         <v>8961808114</v>
@@ -3062,48 +3152,48 @@
         <v>34367</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17">
-      <c r="A26" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" s="11" customFormat="1">
+      <c r="A26" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="C26" s="11" t="s">
+        <v>491</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>488</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="F26" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H26" s="2" t="s">
+      <c r="G26" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="H26" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="L26" s="2">
+      <c r="I26" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="L26" s="11">
         <v>6291885126</v>
       </c>
-      <c r="O26" s="13">
+      <c r="O26" s="20">
         <v>26853</v>
       </c>
-      <c r="Q26" s="2" t="s">
-        <v>265</v>
+      <c r="Q26" s="11" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -3117,25 +3207,25 @@
         <v>52</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L27" s="2">
         <v>8768970820</v>
@@ -3158,25 +3248,25 @@
         <v>52</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L28" s="2">
         <v>9830633996</v>
@@ -3193,31 +3283,31 @@
         <v>78</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L29" s="2">
         <v>7890320765</v>
@@ -3234,31 +3324,31 @@
         <v>78</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E30" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>460</v>
-      </c>
       <c r="I30" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L30" s="2">
         <v>6289023341</v>
@@ -3275,31 +3365,31 @@
         <v>78</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D31" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="I31" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L31" s="2">
         <v>8013684139</v>
@@ -3308,7 +3398,7 @@
         <v>31413</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -3316,31 +3406,31 @@
         <v>78</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L32" s="2">
         <v>7001178476</v>
@@ -3360,28 +3450,28 @@
         <v>96</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F33" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="I33" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L33" s="2">
         <v>3001001111</v>
@@ -3398,31 +3488,31 @@
         <v>78</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L34" s="2">
         <v>8100688109</v>
@@ -3431,7 +3521,7 @@
         <v>38551</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -3442,28 +3532,28 @@
         <v>96</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L35" s="2">
         <v>9874957032</v>
@@ -3472,7 +3562,7 @@
         <v>38718</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -3480,31 +3570,31 @@
         <v>78</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L36" s="2">
         <v>8410972331</v>
@@ -3513,7 +3603,7 @@
         <v>34704</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -3521,31 +3611,31 @@
         <v>78</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="D37" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L37" s="2">
         <v>9836361777</v>
@@ -3562,31 +3652,31 @@
         <v>78</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="D38" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L38" s="2">
         <v>8158906519</v>
@@ -3606,28 +3696,28 @@
         <v>91</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D39" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="G39" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L39" s="2">
         <v>8538803741</v>
@@ -3647,28 +3737,28 @@
         <v>91</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D40" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="G40" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L40" s="2">
         <v>9382830019</v>
@@ -3688,28 +3778,28 @@
         <v>91</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L41" s="2">
         <v>8240829973</v>
@@ -3729,28 +3819,28 @@
         <v>91</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L42" s="2">
         <v>8167542575</v>
@@ -3759,7 +3849,7 @@
         <v>35611</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="43" spans="1:17">
@@ -3770,28 +3860,28 @@
         <v>91</v>
       </c>
       <c r="C43" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D43" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="E43" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="I43" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L43" s="2">
         <v>9832146049</v>
@@ -3814,25 +3904,25 @@
         <v>55</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F44" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="G44" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="I44" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L44" s="2">
         <v>9064571273</v>
@@ -3841,7 +3931,7 @@
         <v>37711</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="45" spans="1:17">
@@ -3852,28 +3942,28 @@
         <v>79</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D45" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="E45" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="F45" s="2" t="s">
+      <c r="G45" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H45" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="I45" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L45" s="2">
         <v>9609061515</v>
@@ -3890,31 +3980,31 @@
         <v>78</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L46" s="2">
         <v>9330662459</v>
@@ -3931,31 +4021,31 @@
         <v>78</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L47" s="2">
         <v>9088420966</v>
@@ -3972,31 +4062,31 @@
         <v>78</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L48" s="2">
         <v>9593174835</v>
@@ -4005,7 +4095,7 @@
         <v>29587</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="49" spans="1:17">
@@ -4013,31 +4103,31 @@
         <v>78</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L49" s="2">
         <v>8910079184</v>
@@ -4046,7 +4136,7 @@
         <v>32327</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="50" spans="1:17">
@@ -4054,31 +4144,31 @@
         <v>78</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L50" s="2">
         <v>9748004445</v>
@@ -4087,7 +4177,7 @@
         <v>25583</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="51" spans="1:17">
@@ -4095,31 +4185,31 @@
         <v>78</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D51" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="E51" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="F51" s="2" t="s">
+      <c r="G51" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="G51" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="I51" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L51" s="2">
         <v>8777252411</v>
@@ -4139,28 +4229,28 @@
         <v>116</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L52" s="2">
         <v>9088611952</v>
@@ -4169,7 +4259,7 @@
         <v>36161</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="53" spans="1:17">
@@ -4180,28 +4270,28 @@
         <v>107</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L53" s="2">
         <v>8777672065</v>
@@ -4221,28 +4311,28 @@
         <v>79</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>39</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L54" s="2">
         <v>8017543639</v>
@@ -4265,25 +4355,25 @@
         <v>106</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>45</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L55" s="2">
         <v>8017714729</v>
@@ -4292,7 +4382,7 @@
         <v>27395</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="56" spans="1:17">
@@ -4300,31 +4390,31 @@
         <v>78</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E56" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H56" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D56" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="E56" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="I56" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L56" s="2">
         <v>3001001112</v>
@@ -4344,28 +4434,28 @@
         <v>91</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L57" s="2">
         <v>7477849839</v>
@@ -4385,28 +4475,28 @@
         <v>91</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D58" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="E58" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>198</v>
-      </c>
       <c r="G58" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L58" s="2">
         <v>7811906715</v>
@@ -4415,7 +4505,7 @@
         <v>36134</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="59" spans="1:17">
@@ -4423,31 +4513,31 @@
         <v>78</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C59" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D59" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E59" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="F59" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D59" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="E59" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="F59" s="2" t="s">
+      <c r="G59" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H59" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="G59" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="I59" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L59" s="2">
         <v>8918785213</v>
@@ -4464,31 +4554,31 @@
         <v>78</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L60" s="2">
         <v>7980330342</v>
@@ -4497,7 +4587,7 @@
         <v>21200</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="61" spans="1:17">
@@ -4505,31 +4595,31 @@
         <v>78</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L61" s="2">
         <v>7044650230</v>
@@ -4538,7 +4628,7 @@
         <v>23743</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="62" spans="1:17">
@@ -4546,31 +4636,31 @@
         <v>78</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L62" s="2">
         <v>9143620183</v>
@@ -4579,7 +4669,7 @@
         <v>30858</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="63" spans="1:17">
@@ -4590,28 +4680,28 @@
         <v>96</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L63" s="2">
         <v>9832371716</v>
@@ -4628,31 +4718,31 @@
         <v>78</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L64" s="2">
         <v>8918393490</v>
@@ -4661,7 +4751,7 @@
         <v>31963</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="65" spans="1:17">
@@ -4672,28 +4762,28 @@
         <v>116</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L65" s="2">
         <v>9748864474</v>
@@ -4702,7 +4792,7 @@
         <v>33360</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="66" spans="1:17">
@@ -4713,28 +4803,28 @@
         <v>79</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>42</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L66" s="2">
         <v>6290396924</v>
@@ -4743,7 +4833,7 @@
         <v>32874</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="67" spans="1:17">
@@ -4751,31 +4841,31 @@
         <v>78</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L67" s="2">
         <v>9088160504</v>
@@ -4792,31 +4882,31 @@
         <v>78</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L68" s="2">
         <v>6296737598</v>
@@ -4833,31 +4923,31 @@
         <v>78</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L69" s="2">
         <v>8101302863</v>
@@ -4869,44 +4959,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="70" spans="1:17">
-      <c r="A70" s="2" t="s">
+    <row r="70" spans="1:17" s="11" customFormat="1">
+      <c r="A70" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>461</v>
+      </c>
+      <c r="D70" s="19" t="s">
+        <v>488</v>
+      </c>
+      <c r="E70" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="F70" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="D70" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="E70" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="J70" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="L70" s="2">
+      <c r="G70" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="H70" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="I70" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="J70" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="L70" s="11">
         <v>8116872785</v>
       </c>
-      <c r="O70" s="13">
+      <c r="O70" s="20">
         <v>38175</v>
       </c>
-      <c r="Q70" s="2" t="s">
+      <c r="Q70" s="11" t="s">
         <v>82</v>
       </c>
     </row>
@@ -4918,28 +5008,28 @@
         <v>91</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L71" s="2">
         <v>6294188266</v>
@@ -4948,7 +5038,7 @@
         <v>35629</v>
       </c>
       <c r="Q71" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="72" spans="1:17">
@@ -4956,31 +5046,31 @@
         <v>78</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F72" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H72" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="G72" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>223</v>
-      </c>
       <c r="I72" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L72" s="2">
         <v>7908637451</v>
@@ -5000,28 +5090,28 @@
         <v>79</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L73" s="2">
         <v>7890349029</v>
@@ -5030,7 +5120,7 @@
         <v>36161</v>
       </c>
       <c r="Q73" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="74" spans="1:17">
@@ -5041,28 +5131,28 @@
         <v>107</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H74" s="12" t="s">
         <v>26</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L74" s="2">
         <v>3001001113</v>
@@ -5079,31 +5169,31 @@
         <v>78</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F75" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H75" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="G75" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="I75" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L75" s="2">
         <v>9635067500</v>
@@ -5120,31 +5210,31 @@
         <v>78</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L76" s="2">
         <v>9073566719</v>
@@ -5153,7 +5243,7 @@
         <v>30317</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="77" spans="1:17">
@@ -5161,31 +5251,31 @@
         <v>78</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E77" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>38</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L77" s="2">
         <v>8017104787</v>
@@ -5194,7 +5284,7 @@
         <v>28333</v>
       </c>
       <c r="Q77" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="78" spans="1:17">
@@ -5205,28 +5295,28 @@
         <v>116</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L78" s="2">
         <v>9123679586</v>
@@ -5235,7 +5325,7 @@
         <v>34065</v>
       </c>
       <c r="Q78" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="79" spans="1:17">
@@ -5243,31 +5333,31 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="D79" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E79" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L79" s="2">
         <v>9735376431</v>
@@ -5287,28 +5377,28 @@
         <v>91</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F80" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H80" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>236</v>
-      </c>
       <c r="I80" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L80" s="2">
         <v>8927482764</v>
@@ -5317,7 +5407,7 @@
         <v>37691</v>
       </c>
       <c r="Q80" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="81" spans="1:17">
@@ -5325,31 +5415,31 @@
         <v>78</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E81" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F81" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H81" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="G81" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="I81" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L81" s="2">
         <v>9163964242</v>
@@ -5366,31 +5456,31 @@
         <v>78</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L82" s="2">
         <v>9732339824</v>
@@ -5410,28 +5500,28 @@
         <v>79</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L83" s="2">
         <v>9003604029</v>
@@ -5451,28 +5541,28 @@
         <v>79</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L84" s="2">
         <v>9804115345</v>
@@ -5481,7 +5571,7 @@
         <v>33353</v>
       </c>
       <c r="Q84" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="85" spans="1:17">
@@ -5495,25 +5585,25 @@
         <v>80</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E85" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L85" s="2">
         <v>8697083089</v>
@@ -5522,7 +5612,7 @@
         <v>38718</v>
       </c>
       <c r="Q85" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="86" spans="1:17">
@@ -5530,31 +5620,31 @@
         <v>78</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E86" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L86" s="2">
         <v>8250187258</v>
@@ -5563,7 +5653,7 @@
         <v>31111</v>
       </c>
       <c r="Q86" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="87" spans="1:17">
@@ -5577,25 +5667,25 @@
         <v>115</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E87" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F87" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H87" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="G87" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>271</v>
-      </c>
       <c r="I87" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L87" s="2">
         <v>9123639488</v>
@@ -5604,7 +5694,7 @@
         <v>31432</v>
       </c>
       <c r="Q87" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="88" spans="1:17">
@@ -5615,28 +5705,28 @@
         <v>116</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L88" s="2">
         <v>8910573289</v>
@@ -5645,7 +5735,7 @@
         <v>28356</v>
       </c>
       <c r="Q88" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="89" spans="1:17">
@@ -5659,25 +5749,25 @@
         <v>115</v>
       </c>
       <c r="D89" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E89" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L89" s="2">
         <v>7890889928</v>
@@ -5694,31 +5784,31 @@
         <v>78</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E90" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F90" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H90" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="G90" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>275</v>
-      </c>
       <c r="I90" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L90" s="2">
         <v>9330686296</v>
@@ -5727,7 +5817,7 @@
         <v>21551</v>
       </c>
       <c r="Q90" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="91" spans="1:17">
@@ -5735,31 +5825,31 @@
         <v>78</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L91" s="2">
         <v>9123829763</v>
@@ -5768,7 +5858,7 @@
         <v>31675</v>
       </c>
       <c r="Q91" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="92" spans="1:17">
@@ -5776,31 +5866,31 @@
         <v>78</v>
       </c>
       <c r="B92" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="D92" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E92" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F92" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H92" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="G92" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>280</v>
-      </c>
       <c r="I92" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L92" s="2">
         <v>9874020651</v>
@@ -5809,7 +5899,7 @@
         <v>38718</v>
       </c>
       <c r="Q92" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="93" spans="1:17">
@@ -5820,28 +5910,28 @@
         <v>79</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D93" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E93" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L93" s="2">
         <v>3001001114</v>
@@ -5850,7 +5940,7 @@
         <v>38718</v>
       </c>
       <c r="Q93" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="94" spans="1:17">
@@ -5858,31 +5948,31 @@
         <v>78</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E94" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L94" s="2">
         <v>8389962917</v>
@@ -5891,7 +5981,7 @@
         <v>31533</v>
       </c>
       <c r="Q94" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="95" spans="1:17">
@@ -5905,25 +5995,25 @@
         <v>115</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E95" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L95" s="2">
         <v>9874701213</v>
@@ -5940,31 +6030,31 @@
         <v>78</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D96" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E96" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F96" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H96" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G96" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>286</v>
-      </c>
       <c r="I96" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L96" s="2">
         <v>7595038331</v>
@@ -5981,31 +6071,31 @@
         <v>78</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D97" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L97" s="2">
         <v>6297317506</v>
@@ -6017,45 +6107,45 @@
         <v>82</v>
       </c>
     </row>
-    <row r="98" spans="1:17">
-      <c r="A98" s="2" t="s">
+    <row r="98" spans="1:17" s="11" customFormat="1">
+      <c r="A98" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="B98" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D98" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="E98" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="F98" s="2" t="s">
+      <c r="C98" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="D98" s="19" t="s">
+        <v>488</v>
+      </c>
+      <c r="E98" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="F98" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="G98" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="H98" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="G98" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="J98" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="L98" s="2">
+      <c r="I98" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="J98" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="L98" s="11">
         <v>9732599639</v>
       </c>
-      <c r="O98" s="13">
+      <c r="O98" s="20">
         <v>34787</v>
       </c>
-      <c r="Q98" s="2" t="s">
-        <v>265</v>
+      <c r="Q98" s="11" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="99" spans="1:17">
@@ -6063,31 +6153,31 @@
         <v>78</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E99" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L99" s="2">
         <v>7278380378</v>
@@ -6096,7 +6186,7 @@
         <v>35482</v>
       </c>
       <c r="Q99" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="100" spans="1:17">
@@ -6110,25 +6200,25 @@
         <v>115</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L100" s="2">
         <v>6290768388</v>
@@ -6148,28 +6238,28 @@
         <v>116</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E101" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F101" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H101" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="G101" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>294</v>
-      </c>
       <c r="I101" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L101" s="2">
         <v>7719191453</v>
@@ -6189,28 +6279,28 @@
         <v>116</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F102" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H102" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="G102" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>297</v>
-      </c>
       <c r="I102" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L102" s="2">
         <v>7439121779</v>
@@ -6230,28 +6320,28 @@
         <v>116</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E103" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F103" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H103" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="G103" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>299</v>
-      </c>
       <c r="I103" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L103" s="2">
         <v>9477941035</v>
@@ -6260,7 +6350,7 @@
         <v>36235</v>
       </c>
       <c r="Q103" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="104" spans="1:17">
@@ -6271,28 +6361,28 @@
         <v>116</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D104" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E104" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L104" s="2">
         <v>8100649226</v>
@@ -6312,28 +6402,28 @@
         <v>116</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D105" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E105" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L105" s="2">
         <v>8972391318</v>
@@ -6356,25 +6446,25 @@
         <v>53</v>
       </c>
       <c r="D106" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E106" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L106" s="2">
         <v>9734427068</v>
@@ -6383,7 +6473,7 @@
         <v>32509</v>
       </c>
       <c r="Q106" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="107" spans="1:17">
@@ -6397,25 +6487,25 @@
         <v>53</v>
       </c>
       <c r="D107" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E107" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L107" s="2">
         <v>9064748123</v>
@@ -6424,7 +6514,7 @@
         <v>30317</v>
       </c>
       <c r="Q107" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="108" spans="1:17">
@@ -6432,31 +6522,31 @@
         <v>78</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D108" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E108" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L108" s="2">
         <v>9732632325</v>
@@ -6465,7 +6555,7 @@
         <v>30348</v>
       </c>
       <c r="Q108" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="109" spans="1:17">
@@ -6473,31 +6563,31 @@
         <v>78</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D109" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E109" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L109" s="2">
         <v>7980520890</v>
@@ -6520,25 +6610,25 @@
         <v>83</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E110" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L110" s="2">
         <v>8584986362</v>
@@ -6561,25 +6651,25 @@
         <v>83</v>
       </c>
       <c r="D111" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E111" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L111" s="2">
         <v>8748069981</v>
@@ -6602,25 +6692,25 @@
         <v>83</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E112" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>47</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L112" s="2">
         <v>9163739332</v>
@@ -6629,7 +6719,7 @@
         <v>33333</v>
       </c>
       <c r="Q112" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="113" spans="1:17">
@@ -6640,28 +6730,28 @@
         <v>79</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E113" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F113" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H113" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="G113" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>313</v>
-      </c>
       <c r="I113" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L113" s="2">
         <v>6297379492</v>
@@ -6678,31 +6768,31 @@
         <v>78</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D114" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E114" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F114" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H114" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="G114" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>315</v>
-      </c>
       <c r="I114" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L114" s="2">
         <v>8582826180</v>
@@ -6719,31 +6809,31 @@
         <v>78</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D115" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E115" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F115" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H115" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="G115" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>317</v>
-      </c>
       <c r="I115" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L115" s="2">
         <v>8017842539</v>
@@ -6760,31 +6850,31 @@
         <v>78</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D116" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E116" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>30</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L116" s="2">
         <v>3111100022</v>
@@ -6793,7 +6883,7 @@
         <v>32874</v>
       </c>
       <c r="Q116" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="117" spans="1:17">
@@ -6801,31 +6891,31 @@
         <v>78</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C117" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D117" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E117" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="F117" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D117" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="E117" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>322</v>
-      </c>
       <c r="G117" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L117" s="2">
         <v>6291909258</v>
@@ -6834,7 +6924,7 @@
         <v>28638</v>
       </c>
       <c r="Q117" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="118" spans="1:17">
@@ -6842,31 +6932,31 @@
         <v>78</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C118" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D118" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E118" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="F118" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="D118" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="E118" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>325</v>
-      </c>
       <c r="G118" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L118" s="2">
         <v>9875601944</v>
@@ -6875,7 +6965,7 @@
         <v>38718</v>
       </c>
       <c r="Q118" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="119" spans="1:17">
@@ -6883,31 +6973,31 @@
         <v>78</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E119" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L119" s="2">
         <v>6289109677</v>
@@ -6916,7 +7006,7 @@
         <v>33239</v>
       </c>
       <c r="Q119" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="120" spans="1:17">
@@ -6924,31 +7014,31 @@
         <v>78</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E120" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L120" s="2">
         <v>6291193933</v>
@@ -6968,28 +7058,28 @@
         <v>116</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D121" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E121" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L121" s="2">
         <v>9073861999</v>
@@ -7012,25 +7102,25 @@
         <v>115</v>
       </c>
       <c r="D122" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E122" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>51</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L122" s="2">
         <v>9007823264</v>
@@ -7039,7 +7129,7 @@
         <v>35796</v>
       </c>
       <c r="Q122" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="123" spans="1:17">
@@ -7047,31 +7137,31 @@
         <v>78</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D123" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E123" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L123" s="2">
         <v>7363028815</v>
@@ -7080,7 +7170,7 @@
         <v>23450</v>
       </c>
       <c r="Q123" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="124" spans="1:17">
@@ -7088,31 +7178,31 @@
         <v>78</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D124" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E124" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L124" s="2">
         <v>8017609870</v>
@@ -7129,31 +7219,31 @@
         <v>78</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C125" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D125" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E125" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="F125" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="D125" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="E125" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>341</v>
-      </c>
       <c r="G125" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L125" s="2">
         <v>7439272489</v>
@@ -7162,7 +7252,7 @@
         <v>34876</v>
       </c>
       <c r="Q125" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="126" spans="1:17">
@@ -7170,31 +7260,31 @@
         <v>78</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C126" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D126" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E126" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="F126" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="D126" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="E126" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>346</v>
-      </c>
       <c r="G126" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L126" s="2">
         <v>7318832484</v>
@@ -7203,7 +7293,7 @@
         <v>27760</v>
       </c>
       <c r="Q126" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="127" spans="1:17">
@@ -7211,31 +7301,31 @@
         <v>78</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D127" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E127" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L127" s="2">
         <v>9733477295</v>
@@ -7244,7 +7334,7 @@
         <v>29221</v>
       </c>
       <c r="Q127" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="128" spans="1:17">
@@ -7252,31 +7342,31 @@
         <v>78</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D128" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E128" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F128" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H128" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="G128" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>349</v>
-      </c>
       <c r="I128" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L128" s="2">
         <v>7602682821</v>
@@ -7285,7 +7375,7 @@
         <v>30317</v>
       </c>
       <c r="Q128" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="129" spans="1:17">
@@ -7293,31 +7383,31 @@
         <v>78</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D129" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E129" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F129" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H129" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="G129" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="I129" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L129" s="2">
         <v>7278956090</v>
@@ -7326,7 +7416,7 @@
         <v>29767</v>
       </c>
       <c r="Q129" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="130" spans="1:17">
@@ -7337,28 +7427,28 @@
         <v>91</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D130" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E130" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L130" s="2">
         <v>3111100023</v>
@@ -7375,31 +7465,31 @@
         <v>78</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D131" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E131" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L131" s="2">
         <v>7890742324</v>
@@ -7416,31 +7506,31 @@
         <v>78</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D132" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E132" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L132" s="2">
         <v>9038842738</v>
@@ -7457,31 +7547,31 @@
         <v>78</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D133" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E133" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L133" s="2">
         <v>9064024783</v>
@@ -7498,31 +7588,31 @@
         <v>78</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>83</v>
       </c>
       <c r="D134" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E134" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L134" s="2">
         <v>7044698552</v>
@@ -7539,31 +7629,31 @@
         <v>78</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D135" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E135" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L135" s="2">
         <v>8637826217</v>
@@ -7580,31 +7670,31 @@
         <v>78</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C136" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D136" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E136" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="F136" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="D136" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="E136" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>364</v>
-      </c>
       <c r="G136" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L136" s="2">
         <v>7306265589</v>
@@ -7621,31 +7711,31 @@
         <v>78</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D137" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E137" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L137" s="2">
         <v>8481820843</v>
@@ -7662,31 +7752,31 @@
         <v>78</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D138" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E138" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L138" s="2">
         <v>8509476028</v>
@@ -7703,31 +7793,31 @@
         <v>78</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D139" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E139" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L139" s="2">
         <v>9093289299</v>
@@ -7747,28 +7837,28 @@
         <v>79</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D140" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E140" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L140" s="2">
         <v>9163709428</v>
@@ -7791,25 +7881,25 @@
         <v>53</v>
       </c>
       <c r="D141" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E141" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L141" s="2">
         <v>8926189051</v>
@@ -7818,7 +7908,7 @@
         <v>24473</v>
       </c>
       <c r="Q141" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="142" spans="1:17">
@@ -7829,28 +7919,28 @@
         <v>116</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D142" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E142" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L142" s="2">
         <v>9007200796</v>
@@ -7859,7 +7949,7 @@
         <v>28126</v>
       </c>
       <c r="Q142" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="143" spans="1:17">
@@ -7867,31 +7957,31 @@
         <v>78</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D143" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E143" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L143" s="2">
         <v>9681260473</v>
@@ -7908,31 +7998,31 @@
         <v>78</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D144" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E144" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L144" s="2">
         <v>9073693252</v>
@@ -7949,31 +8039,31 @@
         <v>78</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D145" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E145" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L145" s="2">
         <v>7063315380</v>
@@ -7982,7 +8072,7 @@
         <v>35830</v>
       </c>
       <c r="Q145" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="146" spans="1:17">
@@ -7990,31 +8080,31 @@
         <v>78</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D146" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E146" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I146" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L146" s="2">
         <v>7044768295</v>
@@ -8023,7 +8113,7 @@
         <v>32634</v>
       </c>
       <c r="Q146" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="147" spans="1:17">
@@ -8031,31 +8121,31 @@
         <v>78</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D147" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E147" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I147" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J147" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L147" s="2">
         <v>9804966019</v>
@@ -8064,7 +8154,7 @@
         <v>38718</v>
       </c>
       <c r="Q147" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="148" spans="1:17">
@@ -8075,28 +8165,28 @@
         <v>91</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D148" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E148" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F148" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H148" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="G148" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H148" s="2" t="s">
-        <v>383</v>
-      </c>
       <c r="I148" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J148" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L148" s="2">
         <v>8391893436</v>
@@ -8105,7 +8195,7 @@
         <v>34665</v>
       </c>
       <c r="Q148" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="149" spans="1:17">
@@ -8113,31 +8203,31 @@
         <v>78</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D149" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E149" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L149" s="2">
         <v>8337048171</v>
@@ -8154,31 +8244,31 @@
         <v>78</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D150" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E150" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I150" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L150" s="2">
         <v>9330196901</v>
@@ -8201,25 +8291,25 @@
         <v>108</v>
       </c>
       <c r="D151" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E151" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I151" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L151" s="2">
         <v>9123372152</v>
@@ -8239,28 +8329,28 @@
         <v>116</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D152" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E152" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F152" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H152" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="G152" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H152" s="2" t="s">
-        <v>392</v>
-      </c>
       <c r="I152" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L152" s="2">
         <v>3001001115</v>
@@ -8269,7 +8359,7 @@
         <v>38718</v>
       </c>
       <c r="Q152" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="153" spans="1:17">
@@ -8280,28 +8370,28 @@
         <v>116</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D153" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E153" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>50</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I153" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L153" s="2">
         <v>6289577206</v>
@@ -8310,7 +8400,7 @@
         <v>34734</v>
       </c>
       <c r="Q153" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="154" spans="1:17">
@@ -8321,28 +8411,28 @@
         <v>116</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D154" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E154" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I154" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L154" s="2">
         <v>9330475046</v>
@@ -8351,7 +8441,7 @@
         <v>35647</v>
       </c>
       <c r="Q154" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="155" spans="1:17">
@@ -8362,28 +8452,28 @@
         <v>116</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D155" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E155" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>49</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I155" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L155" s="2">
         <v>8274988670</v>
@@ -8406,25 +8496,25 @@
         <v>115</v>
       </c>
       <c r="D156" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E156" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I156" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L156" s="2">
         <v>9749575149</v>
@@ -8433,7 +8523,7 @@
         <v>37123</v>
       </c>
       <c r="Q156" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="157" spans="1:17">
@@ -8441,31 +8531,31 @@
         <v>78</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D157" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E157" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F157" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H157" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="G157" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H157" s="2" t="s">
-        <v>401</v>
-      </c>
       <c r="I157" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L157" s="2">
         <v>7003475048</v>
@@ -8474,7 +8564,7 @@
         <v>30178</v>
       </c>
       <c r="Q157" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="158" spans="1:17">
@@ -8482,31 +8572,31 @@
         <v>78</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D158" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E158" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I158" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L158" s="2">
         <v>7319432131</v>
@@ -8529,25 +8619,25 @@
         <v>106</v>
       </c>
       <c r="D159" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E159" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I159" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L159" s="2">
         <v>9933964247</v>
@@ -8556,7 +8646,7 @@
         <v>38718</v>
       </c>
       <c r="Q159" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="160" spans="1:17">
@@ -8564,31 +8654,31 @@
         <v>78</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D160" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E160" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I160" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L160" s="2">
         <v>8240082460</v>
@@ -8597,7 +8687,7 @@
         <v>30022</v>
       </c>
       <c r="Q160" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="161" spans="1:17">
@@ -8608,28 +8698,28 @@
         <v>91</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D161" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E161" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>20</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I161" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L161" s="2">
         <v>8145169508</v>
@@ -8646,31 +8736,31 @@
         <v>78</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D162" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E162" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F162" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H162" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="G162" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H162" s="2" t="s">
-        <v>408</v>
-      </c>
       <c r="I162" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L162" s="2">
         <v>7407875441</v>
@@ -8687,31 +8777,31 @@
         <v>78</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D163" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E163" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I163" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L163" s="2">
         <v>8327873601</v>
@@ -8728,31 +8818,31 @@
         <v>78</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D164" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E164" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I164" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L164" s="2">
         <v>9749145756</v>
@@ -8769,31 +8859,31 @@
         <v>78</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D165" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E165" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I165" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J165" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L165" s="2">
         <v>6297748042</v>
@@ -8810,31 +8900,31 @@
         <v>78</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D166" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E166" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I166" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J166" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L166" s="2">
         <v>9144433201</v>
@@ -8851,31 +8941,31 @@
         <v>78</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D167" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E167" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I167" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L167" s="2">
         <v>7044792791</v>
@@ -8884,7 +8974,7 @@
         <v>33182</v>
       </c>
       <c r="Q167" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="168" spans="1:17">
@@ -8892,31 +8982,31 @@
         <v>78</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D168" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E168" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I168" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L168" s="2">
         <v>9088543362</v>
@@ -8925,7 +9015,7 @@
         <v>31970</v>
       </c>
       <c r="Q168" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="169" spans="1:17">
@@ -8936,28 +9026,28 @@
         <v>116</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D169" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E169" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I169" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L169" s="2">
         <v>9051577344</v>
@@ -8966,7 +9056,7 @@
         <v>29447</v>
       </c>
       <c r="Q169" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="170" spans="1:17">
@@ -8974,31 +9064,31 @@
         <v>78</v>
       </c>
       <c r="B170" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D170" s="14" t="s">
         <v>488</v>
       </c>
-      <c r="C170" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D170" s="14" t="s">
-        <v>489</v>
-      </c>
       <c r="E170" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F170" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H170" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="G170" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H170" s="2" t="s">
-        <v>419</v>
-      </c>
       <c r="I170" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L170" s="2">
         <v>9064713152</v>
@@ -9007,7 +9097,7 @@
         <v>35553</v>
       </c>
       <c r="Q170" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="171" spans="1:17">
@@ -9021,25 +9111,25 @@
         <v>52</v>
       </c>
       <c r="D171" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E171" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F171" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H171" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="G171" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H171" s="2" t="s">
-        <v>422</v>
-      </c>
       <c r="I171" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J171" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L171" s="2">
         <v>9836189474</v>
@@ -9048,7 +9138,7 @@
         <v>32613</v>
       </c>
       <c r="Q171" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="172" spans="1:17">
@@ -9062,25 +9152,25 @@
         <v>106</v>
       </c>
       <c r="D172" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E172" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>44</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I172" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J172" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L172" s="2">
         <v>9163928116</v>
@@ -9089,7 +9179,7 @@
         <v>38718</v>
       </c>
       <c r="Q172" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="173" spans="1:17">
@@ -9103,25 +9193,25 @@
         <v>115</v>
       </c>
       <c r="D173" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E173" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I173" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J173" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L173" s="2">
         <v>9830499636</v>
@@ -9138,31 +9228,31 @@
         <v>78</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D174" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E174" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F174" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H174" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="G174" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H174" s="2" t="s">
-        <v>425</v>
-      </c>
       <c r="I174" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J174" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L174" s="2">
         <v>8240569394</v>
@@ -9171,7 +9261,7 @@
         <v>32091</v>
       </c>
       <c r="Q174" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="175" spans="1:17">
@@ -9182,28 +9272,28 @@
         <v>116</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D175" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E175" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I175" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J175" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L175" s="2">
         <v>9830752915</v>
@@ -9212,7 +9302,7 @@
         <v>23389</v>
       </c>
       <c r="Q175" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="176" spans="1:17">
@@ -9223,28 +9313,28 @@
         <v>91</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D176" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E176" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I176" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J176" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L176" s="2">
         <v>8597844845</v>
@@ -9253,7 +9343,7 @@
         <v>32143</v>
       </c>
       <c r="Q176" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="177" spans="1:17">
@@ -9261,31 +9351,31 @@
         <v>78</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D177" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E177" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I177" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J177" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L177" s="2">
         <v>8240273951</v>
@@ -9302,31 +9392,31 @@
         <v>78</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D178" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E178" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I178" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J178" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L178" s="2">
         <v>7595847893</v>
@@ -9343,31 +9433,31 @@
         <v>78</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D179" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E179" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I179" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J179" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L179" s="2">
         <v>9088846722</v>
@@ -9387,28 +9477,28 @@
         <v>116</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D180" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E180" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I180" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L180" s="2">
         <v>9163358345</v>
@@ -9417,7 +9507,7 @@
         <v>33152</v>
       </c>
       <c r="Q180" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="181" spans="1:17">
@@ -9431,25 +9521,25 @@
         <v>115</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E181" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I181" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L181" s="2">
         <v>9088933558</v>
@@ -9469,28 +9559,28 @@
         <v>116</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D182" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E182" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F182" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H182" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="G182" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H182" s="2" t="s">
-        <v>440</v>
-      </c>
       <c r="I182" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L182" s="2">
         <v>7686869224</v>
@@ -9499,7 +9589,7 @@
         <v>35884</v>
       </c>
       <c r="Q182" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="183" spans="1:17">
@@ -9510,28 +9600,28 @@
         <v>116</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D183" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E183" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I183" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J183" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L183" s="2">
         <v>6290445180</v>
@@ -9551,28 +9641,28 @@
         <v>116</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D184" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E184" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I184" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J184" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L184" s="2">
         <v>7278735723</v>
@@ -9581,7 +9671,7 @@
         <v>38718</v>
       </c>
       <c r="Q184" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="185" spans="1:17">
@@ -9589,31 +9679,31 @@
         <v>78</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D185" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E185" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>54</v>
       </c>
       <c r="I185" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J185" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L185" s="2">
         <v>9831806256</v>
@@ -9633,28 +9723,28 @@
         <v>96</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D186" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E186" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I186" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J186" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L186" s="2">
         <v>9635328272</v>
@@ -9671,31 +9761,31 @@
         <v>78</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>113</v>
       </c>
       <c r="D187" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E187" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F187" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H187" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="G187" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H187" s="2" t="s">
-        <v>454</v>
-      </c>
       <c r="I187" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J187" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L187" s="2">
         <v>8697119471</v>
@@ -9704,7 +9794,7 @@
         <v>32143</v>
       </c>
       <c r="Q187" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="188" spans="1:17">
@@ -9715,28 +9805,28 @@
         <v>107</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D188" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E188" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F188" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H188" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="G188" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H188" s="2" t="s">
-        <v>456</v>
-      </c>
       <c r="I188" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J188" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L188" s="2">
         <v>9330534106</v>
@@ -9756,28 +9846,28 @@
         <v>116</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D189" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E189" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I189" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J189" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L189" s="2">
         <v>7278261573</v>
@@ -9786,7 +9876,7 @@
         <v>31048</v>
       </c>
       <c r="Q189" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="190" spans="1:17">
@@ -9794,31 +9884,31 @@
         <v>78</v>
       </c>
       <c r="B190" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C190" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="C190" s="2" t="s">
-        <v>486</v>
-      </c>
       <c r="D190" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E190" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I190" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J190" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L190" s="2">
         <v>8918644453</v>
@@ -29880,9 +29970,774 @@
   <autoFilter ref="A1:X190"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A189"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="41.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="21" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="21" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="21" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="21" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="21" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="21" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="21" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="21" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="21" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="21" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="21" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="21" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="21" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="21" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="21" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="21" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="21" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="21" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="21" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="21" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="21" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="21" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="21" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="21" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="21" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="21" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="21" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="21" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="21" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="21" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="21" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="21" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="21" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="21" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="21" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="21" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="21" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="21" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="2"/>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="2"/>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="2"/>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="2"/>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="2"/>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="2"/>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="2"/>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="2"/>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="2"/>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="2"/>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="2"/>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="2"/>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="2"/>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="2"/>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="2"/>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="2"/>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="2"/>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="2"/>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="2"/>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="2"/>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="2"/>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="2"/>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="2"/>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="2"/>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="2"/>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="2"/>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="2"/>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="2"/>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="2"/>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="2"/>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="2"/>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="2"/>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="2"/>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="2"/>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="2"/>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="2"/>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="2"/>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="2"/>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="2"/>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="2"/>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="2"/>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="2"/>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="2"/>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="2"/>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="2"/>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="2"/>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="2"/>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="2"/>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="2"/>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="2"/>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="2"/>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="2"/>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="2"/>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="2"/>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="2"/>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="2"/>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="2"/>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="2"/>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="2"/>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="2"/>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="2"/>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="2"/>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="2"/>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="2"/>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="2"/>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="2"/>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="2"/>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="2"/>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="2"/>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="2"/>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="2"/>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="2"/>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="2"/>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="2"/>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="2"/>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="2"/>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="2"/>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="2"/>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="2"/>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="2"/>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="2"/>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="2"/>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="2"/>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="2"/>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="2"/>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="2"/>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="2"/>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="2"/>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="2"/>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="2"/>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="2"/>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="2"/>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="2"/>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="2"/>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="2"/>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="2"/>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="2"/>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="2"/>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="2"/>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="2"/>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="2"/>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="2"/>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="2"/>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="2"/>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="2"/>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="2"/>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="2"/>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="2"/>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="2"/>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="2"/>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="2"/>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="2"/>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="2"/>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="2"/>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="2"/>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="2"/>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="2"/>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="2"/>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="2"/>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="2"/>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="2"/>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="2"/>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="2"/>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="2"/>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="2"/>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="2"/>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" s="2"/>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="2"/>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="2"/>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" s="2"/>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="2"/>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="2"/>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="2"/>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="2"/>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="2"/>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="2"/>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="2"/>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" s="2"/>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="2"/>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" s="2"/>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" s="2"/>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" s="2"/>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" s="2"/>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A2:Q3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="1:17" s="2" customFormat="1" ht="12">
+      <c r="A2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="L2" s="2">
+        <v>8637826217</v>
+      </c>
+      <c r="O2" s="13">
+        <v>29952</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" s="2" customFormat="1" ht="12">
+      <c r="A3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>489</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="L3" s="2">
+        <v>9635328272</v>
+      </c>
+      <c r="O3" s="13">
+        <v>34105</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="L2:L3">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>